--- a/StructureDefinition-openelis-patient.xlsx
+++ b/StructureDefinition-openelis-patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.2.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T02:24:20+00:00</t>
+    <t>2026-10-12T15:07:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1232,7 +1232,7 @@
     <t>Administrative Gender - the gender that the patient is considered to have for administration and record keeping purposes.</t>
   </si>
   <si>
-    <t>OpenELIS stores M / F. M maps to male. Any other stored value maps to female. A blank value maps to unknown (see Known Issues).</t>
+    <t>Stored M = male, F = female, O = other. A blank or any other value = unknown.</t>
   </si>
   <si>
     <t>Needed for identification of the individual, in combination with (at least) name and birth date.</t>

--- a/StructureDefinition-openelis-patient.xlsx
+++ b/StructureDefinition-openelis-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T15:07:11+00:00</t>
+    <t>2026-10-12T15:22:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-openelis-patient.xlsx
+++ b/StructureDefinition-openelis-patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.1</t>
+    <t>0.2.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T15:22:52+00:00</t>
+    <t>2026-10-14T21:19:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1205,7 +1205,7 @@
     <t>A contact detail (e.g. a telephone number or an email address) by which the individual may be contacted.</t>
   </si>
   <si>
-    <t>Primary phone (use = mobile), email and fax.</t>
+    <t>Primary phone (use = mobile), email and fax. Blank values are not sent.</t>
   </si>
   <si>
     <t>People have (primary) ways to contact them in some way such as phone, email.</t>
